--- a/src/moodys_datahub/data/products.xlsx
+++ b/src/moodys_datahub/data/products.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/kgp_libas_cbs_dk/Documents/Desktop/moody-s_datahub/src/moodys_datahub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{878F10CF-7955-491B-8F8B-956D1E605C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36065365-E65F-48DE-84A4-6AFEAD8F8A99}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{878F10CF-7955-491B-8F8B-956D1E605C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F3B8166-F407-432B-B67F-8B1EF4841E58}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{95D8BC7B-D8C9-4298-9EA2-4D3ACA8B17DE}"/>
+    <workbookView xWindow="4065" yWindow="4065" windowWidth="21600" windowHeight="11295" xr2:uid="{95D8BC7B-D8C9-4298-9EA2-4D3ACA8B17DE}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">products!$A$1:$D$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">products!$A$1:$D$31</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="45">
   <si>
     <t>Data Product</t>
   </si>
@@ -152,6 +152,12 @@
   </si>
   <si>
     <t>False</t>
+  </si>
+  <si>
+    <t>links_2023</t>
+  </si>
+  <si>
+    <t>links_2024</t>
   </si>
 </sst>
 </file>
@@ -1018,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F40E21F1-55D6-4BB0-8DC1-F9616B9C9916}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.5703125" customWidth="1"/>
@@ -1423,19 +1429,47 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" t="s">
         <v>27</v>
       </c>
-      <c r="C29" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="C31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D29" xr:uid="{F40E21F1-55D6-4BB0-8DC1-F9616B9C9916}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D29">
-      <sortCondition ref="D1:D29"/>
+  <autoFilter ref="A1:D31" xr:uid="{F40E21F1-55D6-4BB0-8DC1-F9616B9C9916}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D31">
+      <sortCondition ref="D1:D31"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="18" type="noConversion"/>

--- a/src/moodys_datahub/data/products.xlsx
+++ b/src/moodys_datahub/data/products.xlsx
@@ -16,7 +16,7 @@
     <sheet name="products" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">products!$A$1:$D$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">products!$A$1:$D$32</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -1024,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F40E21F1-55D6-4BB0-8DC1-F9616B9C9916}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.5703125" customWidth="1"/>
@@ -1466,10 +1466,26 @@
         <v>41</v>
       </c>
     </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">links_2025</t>
+        </is>
+      </c>
+      <c r="C32" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D31" xr:uid="{F40E21F1-55D6-4BB0-8DC1-F9616B9C9916}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D31">
-      <sortCondition ref="D1:D31"/>
+  <autoFilter ref="A1:D32" xr:uid="{F40E21F1-55D6-4BB0-8DC1-F9616B9C9916}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D32">
+      <sortCondition ref="D1:D32"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="18" type="noConversion"/>
